--- a/output/yearly_population_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_14_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4767</v>
+        <v>8752</v>
       </c>
       <c r="C2" t="n">
-        <v>6509</v>
+        <v>3990</v>
       </c>
       <c r="D2" t="n">
-        <v>23426</v>
+        <v>32670</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3153</v>
+        <v>4825</v>
       </c>
       <c r="C3" t="n">
-        <v>3895</v>
+        <v>4155</v>
       </c>
       <c r="D3" t="n">
-        <v>13585</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2618</v>
+        <v>3198</v>
       </c>
       <c r="C4" t="n">
-        <v>5104</v>
+        <v>4916</v>
       </c>
       <c r="D4" t="n">
-        <v>7138</v>
+        <v>7326</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>4017</v>
+        <v>3155</v>
       </c>
       <c r="D5" t="n">
-        <v>2864</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="n">
-        <v>2337</v>
+        <v>1596</v>
       </c>
       <c r="D6" t="n">
-        <v>1226</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>483</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>1251</v>
+        <v>949</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>513</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6600</v>
+        <v>9802</v>
       </c>
       <c r="C2" t="n">
-        <v>6266</v>
+        <v>9136</v>
       </c>
       <c r="D2" t="n">
-        <v>24591</v>
+        <v>24380</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3171</v>
+        <v>5382</v>
       </c>
       <c r="C3" t="n">
-        <v>4502</v>
+        <v>3574</v>
       </c>
       <c r="D3" t="n">
-        <v>14067</v>
+        <v>19234</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2448</v>
+        <v>3389</v>
       </c>
       <c r="C4" t="n">
-        <v>4345</v>
+        <v>4386</v>
       </c>
       <c r="D4" t="n">
-        <v>8035</v>
+        <v>9026</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1864</v>
+        <v>2288</v>
       </c>
       <c r="C5" t="n">
-        <v>4465</v>
+        <v>3951</v>
       </c>
       <c r="D5" t="n">
-        <v>3446</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1202</v>
+        <v>1451</v>
       </c>
       <c r="C6" t="n">
-        <v>3103</v>
+        <v>2297</v>
       </c>
       <c r="D6" t="n">
-        <v>1476</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>633</v>
+        <v>759</v>
       </c>
       <c r="C7" t="n">
-        <v>1738</v>
+        <v>1252</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>704</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
         <v>129</v>
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8102</v>
+        <v>10991</v>
       </c>
       <c r="C2" t="n">
-        <v>10743</v>
+        <v>11198</v>
       </c>
       <c r="D2" t="n">
-        <v>23176</v>
+        <v>28501</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3733</v>
+        <v>5887</v>
       </c>
       <c r="C3" t="n">
-        <v>4653</v>
+        <v>5292</v>
       </c>
       <c r="D3" t="n">
-        <v>14491</v>
+        <v>18630</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2352</v>
+        <v>3595</v>
       </c>
       <c r="C4" t="n">
-        <v>4285</v>
+        <v>3878</v>
       </c>
       <c r="D4" t="n">
-        <v>8640</v>
+        <v>10232</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>2436</v>
       </c>
       <c r="C5" t="n">
-        <v>4317</v>
+        <v>4065</v>
       </c>
       <c r="D5" t="n">
-        <v>4046</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1348</v>
+        <v>1661</v>
       </c>
       <c r="C6" t="n">
-        <v>3631</v>
+        <v>2967</v>
       </c>
       <c r="D6" t="n">
-        <v>1725</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>780</v>
+        <v>938</v>
       </c>
       <c r="C7" t="n">
-        <v>2325</v>
+        <v>1702</v>
       </c>
       <c r="D7" t="n">
-        <v>845</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>373</v>
+        <v>439</v>
       </c>
       <c r="C8" t="n">
-        <v>1229</v>
+        <v>922</v>
       </c>
       <c r="D8" t="n">
-        <v>500</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C9" t="n">
-        <v>612</v>
+        <v>509</v>
       </c>
       <c r="D9" t="n">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
         <v>131</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1604,7 +1604,7 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7223</v>
+        <v>9960</v>
       </c>
       <c r="C2" t="n">
-        <v>7047</v>
+        <v>7345</v>
       </c>
       <c r="D2" t="n">
-        <v>18911</v>
+        <v>23288</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4452</v>
+        <v>6925</v>
       </c>
       <c r="C3" t="n">
-        <v>7659</v>
+        <v>8181</v>
       </c>
       <c r="D3" t="n">
-        <v>16111</v>
+        <v>20442</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1753</v>
+        <v>2250</v>
       </c>
       <c r="C4" t="n">
-        <v>6612</v>
+        <v>6136</v>
       </c>
       <c r="D4" t="n">
-        <v>8480</v>
+        <v>9507</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1245</v>
+        <v>1534</v>
       </c>
       <c r="C5" t="n">
-        <v>3558</v>
+        <v>2907</v>
       </c>
       <c r="D5" t="n">
-        <v>2816</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>720</v>
+        <v>866</v>
       </c>
       <c r="C6" t="n">
-        <v>2278</v>
+        <v>1667</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="C7" t="n">
-        <v>1204</v>
+        <v>903</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>599</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
         <v>204</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>128</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1901,7 +1901,7 @@
         <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>39</v>
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4310</v>
+        <v>5877</v>
       </c>
       <c r="C2" t="n">
-        <v>3394</v>
+        <v>3751</v>
       </c>
       <c r="D2" t="n">
-        <v>13980</v>
+        <v>17314</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4854</v>
+        <v>7122</v>
       </c>
       <c r="C3" t="n">
-        <v>6647</v>
+        <v>7021</v>
       </c>
       <c r="D3" t="n">
-        <v>15715</v>
+        <v>19837</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2455</v>
+        <v>3523</v>
       </c>
       <c r="C4" t="n">
-        <v>7240</v>
+        <v>7245</v>
       </c>
       <c r="D4" t="n">
-        <v>9475</v>
+        <v>10988</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>4974</v>
+        <v>4380</v>
       </c>
       <c r="D5" t="n">
-        <v>3572</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>2860</v>
+        <v>2204</v>
       </c>
       <c r="D6" t="n">
-        <v>1033</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>327</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>1625</v>
+        <v>1206</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>799</v>
+        <v>648</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2198,7 +2198,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5211</v>
+        <v>6142</v>
       </c>
       <c r="C2" t="n">
-        <v>5519</v>
+        <v>6825</v>
       </c>
       <c r="D2" t="n">
-        <v>23563</v>
+        <v>24343</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3908</v>
+        <v>5527</v>
       </c>
       <c r="C3" t="n">
-        <v>4401</v>
+        <v>4788</v>
       </c>
       <c r="D3" t="n">
-        <v>14383</v>
+        <v>18108</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3012</v>
+        <v>4380</v>
       </c>
       <c r="C4" t="n">
-        <v>6851</v>
+        <v>6980</v>
       </c>
       <c r="D4" t="n">
-        <v>10265</v>
+        <v>12183</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1648</v>
+        <v>2217</v>
       </c>
       <c r="C5" t="n">
-        <v>5979</v>
+        <v>5691</v>
       </c>
       <c r="D5" t="n">
-        <v>4426</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>1244</v>
       </c>
       <c r="C6" t="n">
-        <v>3853</v>
+        <v>3226</v>
       </c>
       <c r="D6" t="n">
-        <v>1409</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>2197</v>
+        <v>1667</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>1154</v>
+        <v>889</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
         <v>136</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2509,7 +2509,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3008</v>
+        <v>3589</v>
       </c>
       <c r="C2" t="n">
-        <v>2490</v>
+        <v>3082</v>
       </c>
       <c r="D2" t="n">
-        <v>16245</v>
+        <v>16847</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4089</v>
+        <v>5525</v>
       </c>
       <c r="C3" t="n">
-        <v>4604</v>
+        <v>5344</v>
       </c>
       <c r="D3" t="n">
-        <v>15065</v>
+        <v>18371</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3373</v>
+        <v>4827</v>
       </c>
       <c r="C4" t="n">
-        <v>6561</v>
+        <v>6747</v>
       </c>
       <c r="D4" t="n">
-        <v>10840</v>
+        <v>12966</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>2279</v>
       </c>
       <c r="C5" t="n">
-        <v>6972</v>
+        <v>6815</v>
       </c>
       <c r="D5" t="n">
-        <v>4781</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>1061</v>
       </c>
       <c r="C6" t="n">
-        <v>4767</v>
+        <v>3907</v>
       </c>
       <c r="D6" t="n">
-        <v>1384</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>2264</v>
+        <v>1727</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>899</v>
+        <v>743</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2806,7 +2806,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>36</v>
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3706</v>
+        <v>4573</v>
       </c>
       <c r="C2" t="n">
-        <v>3587</v>
+        <v>8461</v>
       </c>
       <c r="D2" t="n">
-        <v>13721</v>
+        <v>14668</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3090</v>
+        <v>3983</v>
       </c>
       <c r="C3" t="n">
-        <v>3201</v>
+        <v>3795</v>
       </c>
       <c r="D3" t="n">
-        <v>14343</v>
+        <v>17063</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3238</v>
+        <v>4520</v>
       </c>
       <c r="C4" t="n">
-        <v>5466</v>
+        <v>5984</v>
       </c>
       <c r="D4" t="n">
-        <v>11199</v>
+        <v>13453</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2149</v>
+        <v>2932</v>
       </c>
       <c r="C5" t="n">
-        <v>6700</v>
+        <v>6707</v>
       </c>
       <c r="D5" t="n">
-        <v>5566</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1110</v>
+        <v>1400</v>
       </c>
       <c r="C6" t="n">
-        <v>5788</v>
+        <v>5164</v>
       </c>
       <c r="D6" t="n">
-        <v>1868</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>3315</v>
+        <v>2657</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>1446</v>
+        <v>1123</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
         <v>101</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2657</v>
+        <v>3315</v>
       </c>
       <c r="C2" t="n">
-        <v>2071</v>
+        <v>4293</v>
       </c>
       <c r="D2" t="n">
-        <v>10803</v>
+        <v>11204</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2887</v>
+        <v>3661</v>
       </c>
       <c r="C3" t="n">
-        <v>3069</v>
+        <v>5153</v>
       </c>
       <c r="D3" t="n">
-        <v>13597</v>
+        <v>15847</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2939</v>
+        <v>4012</v>
       </c>
       <c r="C4" t="n">
-        <v>4500</v>
+        <v>5107</v>
       </c>
       <c r="D4" t="n">
-        <v>11388</v>
+        <v>13658</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2369</v>
+        <v>3254</v>
       </c>
       <c r="C5" t="n">
-        <v>6344</v>
+        <v>6554</v>
       </c>
       <c r="D5" t="n">
-        <v>6099</v>
+        <v>6897</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1302</v>
+        <v>1673</v>
       </c>
       <c r="C6" t="n">
-        <v>6327</v>
+        <v>5869</v>
       </c>
       <c r="D6" t="n">
-        <v>2255</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>4195</v>
+        <v>3476</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1916</v>
+        <v>1489</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>519</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4403</v>
+        <v>6372</v>
       </c>
       <c r="C2" t="n">
-        <v>12970</v>
+        <v>8732</v>
       </c>
       <c r="D2" t="n">
-        <v>19303</v>
+        <v>11942</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2354</v>
+        <v>2972</v>
       </c>
       <c r="C3" t="n">
-        <v>2369</v>
+        <v>4251</v>
       </c>
       <c r="D3" t="n">
-        <v>12347</v>
+        <v>14365</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2562</v>
+        <v>3375</v>
       </c>
       <c r="C4" t="n">
-        <v>3774</v>
+        <v>5021</v>
       </c>
       <c r="D4" t="n">
-        <v>11381</v>
+        <v>13426</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2343</v>
+        <v>3240</v>
       </c>
       <c r="C5" t="n">
-        <v>5433</v>
+        <v>5806</v>
       </c>
       <c r="D5" t="n">
-        <v>6675</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1564</v>
+        <v>2059</v>
       </c>
       <c r="C6" t="n">
-        <v>6278</v>
+        <v>6093</v>
       </c>
       <c r="D6" t="n">
-        <v>2742</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="C7" t="n">
-        <v>5029</v>
+        <v>4446</v>
       </c>
       <c r="D7" t="n">
-        <v>965</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>2782</v>
+        <v>2208</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1060</v>
+        <v>856</v>
       </c>
       <c r="D9" t="n">
         <v>309</v>
@@ -3694,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
         <v>39</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5105</v>
+        <v>6565</v>
       </c>
       <c r="C2" t="n">
-        <v>4500</v>
+        <v>3672</v>
       </c>
       <c r="D2" t="n">
-        <v>12526</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3114</v>
+        <v>4509</v>
       </c>
       <c r="C2" t="n">
-        <v>7160</v>
+        <v>4889</v>
       </c>
       <c r="D2" t="n">
-        <v>14208</v>
+        <v>8790</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3214</v>
+        <v>4179</v>
       </c>
       <c r="C3" t="n">
-        <v>5195</v>
+        <v>5686</v>
       </c>
       <c r="D3" t="n">
-        <v>13744</v>
+        <v>15456</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3475</v>
+        <v>4714</v>
       </c>
       <c r="C4" t="n">
-        <v>5535</v>
+        <v>7037</v>
       </c>
       <c r="D4" t="n">
-        <v>11808</v>
+        <v>13751</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1531</v>
+        <v>2022</v>
       </c>
       <c r="C5" t="n">
-        <v>8397</v>
+        <v>8563</v>
       </c>
       <c r="D5" t="n">
-        <v>6213</v>
+        <v>6975</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>544</v>
+        <v>660</v>
       </c>
       <c r="C6" t="n">
-        <v>6281</v>
+        <v>5611</v>
       </c>
       <c r="D6" t="n">
-        <v>2156</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2726</v>
+        <v>2163</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1038</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
         <v>302</v>
@@ -4302,10 +4302,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
         <v>38</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6782</v>
+        <v>6748</v>
       </c>
       <c r="C2" t="n">
-        <v>3103</v>
+        <v>2330</v>
       </c>
       <c r="D2" t="n">
-        <v>19409</v>
+        <v>12762</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2170</v>
+        <v>2789</v>
       </c>
       <c r="C3" t="n">
-        <v>2268</v>
+        <v>1880</v>
       </c>
       <c r="D3" t="n">
-        <v>2743</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4259</v>
+        <v>4728</v>
       </c>
       <c r="C2" t="n">
-        <v>3812</v>
+        <v>3134</v>
       </c>
       <c r="D2" t="n">
-        <v>20384</v>
+        <v>13733</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3672</v>
+        <v>3917</v>
       </c>
       <c r="C3" t="n">
-        <v>2363</v>
+        <v>1841</v>
       </c>
       <c r="D3" t="n">
-        <v>5341</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>976</v>
+        <v>1245</v>
       </c>
       <c r="C4" t="n">
-        <v>1373</v>
+        <v>1162</v>
       </c>
       <c r="D4" t="n">
-        <v>1734</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5131</v>
+        <v>6515</v>
       </c>
       <c r="C2" t="n">
-        <v>7421</v>
+        <v>3222</v>
       </c>
       <c r="D2" t="n">
-        <v>19222</v>
+        <v>24569</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3265</v>
+        <v>3559</v>
       </c>
       <c r="C3" t="n">
-        <v>2729</v>
+        <v>2211</v>
       </c>
       <c r="D3" t="n">
-        <v>7363</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1965</v>
+        <v>2220</v>
       </c>
       <c r="C4" t="n">
-        <v>1905</v>
+        <v>1528</v>
       </c>
       <c r="D4" t="n">
-        <v>2373</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>461</v>
+        <v>570</v>
       </c>
       <c r="C5" t="n">
-        <v>844</v>
+        <v>739</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>625</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4757</v>
+        <v>6369</v>
       </c>
       <c r="C2" t="n">
-        <v>5523</v>
+        <v>4819</v>
       </c>
       <c r="D2" t="n">
-        <v>29798</v>
+        <v>23088</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3403</v>
+        <v>4078</v>
       </c>
       <c r="C3" t="n">
-        <v>4510</v>
+        <v>2381</v>
       </c>
       <c r="D3" t="n">
-        <v>8647</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2211</v>
+        <v>2476</v>
       </c>
       <c r="C4" t="n">
-        <v>2316</v>
+        <v>1869</v>
       </c>
       <c r="D4" t="n">
-        <v>3188</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1008</v>
+        <v>1159</v>
       </c>
       <c r="C5" t="n">
-        <v>1386</v>
+        <v>1133</v>
       </c>
       <c r="D5" t="n">
-        <v>1407</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>571</v>
+        <v>525</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
         <v>668</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6023</v>
+        <v>6930</v>
       </c>
       <c r="C2" t="n">
-        <v>9304</v>
+        <v>8781</v>
       </c>
       <c r="D2" t="n">
-        <v>23072</v>
+        <v>36013</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2969</v>
+        <v>3816</v>
       </c>
       <c r="C3" t="n">
-        <v>4123</v>
+        <v>3006</v>
       </c>
       <c r="D3" t="n">
-        <v>10586</v>
+        <v>8887</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1741</v>
+        <v>2061</v>
       </c>
       <c r="C4" t="n">
-        <v>2909</v>
+        <v>1774</v>
       </c>
       <c r="D4" t="n">
-        <v>3538</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>852</v>
+        <v>957</v>
       </c>
       <c r="C5" t="n">
-        <v>1362</v>
+        <v>1118</v>
       </c>
       <c r="D5" t="n">
-        <v>1369</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>667</v>
+        <v>561</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
         <v>361</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4912</v>
+        <v>6338</v>
       </c>
       <c r="C2" t="n">
-        <v>6345</v>
+        <v>7256</v>
       </c>
       <c r="D2" t="n">
-        <v>22010</v>
+        <v>35855</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>4489</v>
       </c>
       <c r="C3" t="n">
-        <v>6223</v>
+        <v>5576</v>
       </c>
       <c r="D3" t="n">
-        <v>11987</v>
+        <v>12992</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2077</v>
+        <v>2580</v>
       </c>
       <c r="C4" t="n">
-        <v>3606</v>
+        <v>2505</v>
       </c>
       <c r="D4" t="n">
-        <v>4918</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1157</v>
+        <v>1363</v>
       </c>
       <c r="C5" t="n">
-        <v>2269</v>
+        <v>1491</v>
       </c>
       <c r="D5" t="n">
-        <v>1751</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>618</v>
       </c>
       <c r="C6" t="n">
-        <v>1065</v>
+        <v>880</v>
       </c>
       <c r="D6" t="n">
-        <v>881</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D8" t="n">
         <v>384</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4055</v>
+        <v>7480</v>
       </c>
       <c r="C2" t="n">
-        <v>3580</v>
+        <v>4019</v>
       </c>
       <c r="D2" t="n">
-        <v>23368</v>
+        <v>40217</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3607</v>
+        <v>4459</v>
       </c>
       <c r="C3" t="n">
-        <v>5426</v>
+        <v>5628</v>
       </c>
       <c r="D3" t="n">
-        <v>12903</v>
+        <v>15876</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2506</v>
+        <v>3071</v>
       </c>
       <c r="C4" t="n">
-        <v>5063</v>
+        <v>4251</v>
       </c>
       <c r="D4" t="n">
-        <v>6078</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1433</v>
+        <v>1731</v>
       </c>
       <c r="C5" t="n">
-        <v>2979</v>
+        <v>2020</v>
       </c>
       <c r="D5" t="n">
-        <v>2305</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>773</v>
+        <v>912</v>
       </c>
       <c r="C6" t="n">
-        <v>1711</v>
+        <v>1209</v>
       </c>
       <c r="D6" t="n">
-        <v>1018</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="C7" t="n">
-        <v>808</v>
+        <v>681</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">

--- a/output/yearly_population_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_14_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8752</v>
+        <v>5288</v>
       </c>
       <c r="C2" t="n">
-        <v>3990</v>
+        <v>10736</v>
       </c>
       <c r="D2" t="n">
-        <v>32670</v>
+        <v>26752</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4825</v>
+        <v>3566</v>
       </c>
       <c r="C3" t="n">
-        <v>4155</v>
+        <v>6347</v>
       </c>
       <c r="D3" t="n">
-        <v>18458</v>
+        <v>14592</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3198</v>
+        <v>2974</v>
       </c>
       <c r="C4" t="n">
-        <v>4916</v>
+        <v>4155</v>
       </c>
       <c r="D4" t="n">
-        <v>7326</v>
+        <v>7081</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>1818</v>
       </c>
       <c r="C5" t="n">
-        <v>3155</v>
+        <v>3441</v>
       </c>
       <c r="D5" t="n">
-        <v>2529</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1184</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>1596</v>
+        <v>2356</v>
       </c>
       <c r="D6" t="n">
-        <v>1072</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>949</v>
+        <v>1274</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>513</v>
+        <v>563</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9802</v>
+        <v>7685</v>
       </c>
       <c r="C2" t="n">
-        <v>9136</v>
+        <v>14582</v>
       </c>
       <c r="D2" t="n">
-        <v>24380</v>
+        <v>25140</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5382</v>
+        <v>3593</v>
       </c>
       <c r="C3" t="n">
-        <v>3574</v>
+        <v>7390</v>
       </c>
       <c r="D3" t="n">
-        <v>19234</v>
+        <v>15339</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3389</v>
+        <v>2776</v>
       </c>
       <c r="C4" t="n">
-        <v>4386</v>
+        <v>5122</v>
       </c>
       <c r="D4" t="n">
-        <v>9026</v>
+        <v>8163</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2288</v>
+        <v>2055</v>
       </c>
       <c r="C5" t="n">
-        <v>3951</v>
+        <v>3719</v>
       </c>
       <c r="D5" t="n">
-        <v>3210</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1451</v>
+        <v>1240</v>
       </c>
       <c r="C6" t="n">
-        <v>2297</v>
+        <v>2819</v>
       </c>
       <c r="D6" t="n">
-        <v>1295</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>759</v>
+        <v>624</v>
       </c>
       <c r="C7" t="n">
-        <v>1252</v>
+        <v>1782</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
-        <v>704</v>
+        <v>883</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10991</v>
+        <v>7893</v>
       </c>
       <c r="C2" t="n">
-        <v>11198</v>
+        <v>16904</v>
       </c>
       <c r="D2" t="n">
-        <v>28501</v>
+        <v>25370</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5887</v>
+        <v>4295</v>
       </c>
       <c r="C3" t="n">
-        <v>5292</v>
+        <v>9288</v>
       </c>
       <c r="D3" t="n">
-        <v>18630</v>
+        <v>15587</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3595</v>
+        <v>2690</v>
       </c>
       <c r="C4" t="n">
-        <v>3878</v>
+        <v>6060</v>
       </c>
       <c r="D4" t="n">
-        <v>10232</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2436</v>
+        <v>2095</v>
       </c>
       <c r="C5" t="n">
-        <v>4065</v>
+        <v>4225</v>
       </c>
       <c r="D5" t="n">
-        <v>4005</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1661</v>
+        <v>1435</v>
       </c>
       <c r="C6" t="n">
-        <v>2967</v>
+        <v>3181</v>
       </c>
       <c r="D6" t="n">
-        <v>1540</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>938</v>
+        <v>787</v>
       </c>
       <c r="C7" t="n">
-        <v>1702</v>
+        <v>2200</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C8" t="n">
-        <v>922</v>
+        <v>1244</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>590</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9960</v>
+        <v>7202</v>
       </c>
       <c r="C2" t="n">
-        <v>7345</v>
+        <v>11224</v>
       </c>
       <c r="D2" t="n">
-        <v>23288</v>
+        <v>20691</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6925</v>
+        <v>5072</v>
       </c>
       <c r="C3" t="n">
-        <v>8181</v>
+        <v>13600</v>
       </c>
       <c r="D3" t="n">
-        <v>20442</v>
+        <v>17227</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>1935</v>
       </c>
       <c r="C4" t="n">
-        <v>6136</v>
+        <v>7488</v>
       </c>
       <c r="D4" t="n">
-        <v>9507</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1534</v>
+        <v>1325</v>
       </c>
       <c r="C5" t="n">
-        <v>2907</v>
+        <v>3117</v>
       </c>
       <c r="D5" t="n">
-        <v>2624</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>866</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>1667</v>
+        <v>2156</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>903</v>
+        <v>1219</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>498</v>
+        <v>578</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5877</v>
+        <v>4288</v>
       </c>
       <c r="C2" t="n">
-        <v>3751</v>
+        <v>4596</v>
       </c>
       <c r="D2" t="n">
-        <v>17314</v>
+        <v>16034</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7122</v>
+        <v>5171</v>
       </c>
       <c r="C3" t="n">
-        <v>7021</v>
+        <v>11286</v>
       </c>
       <c r="D3" t="n">
-        <v>19837</v>
+        <v>16871</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3523</v>
+        <v>2732</v>
       </c>
       <c r="C4" t="n">
-        <v>7245</v>
+        <v>10553</v>
       </c>
       <c r="D4" t="n">
-        <v>10988</v>
+        <v>9877</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>1469</v>
       </c>
       <c r="C5" t="n">
-        <v>4380</v>
+        <v>5048</v>
       </c>
       <c r="D5" t="n">
-        <v>3544</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>2204</v>
+        <v>2607</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>1206</v>
+        <v>1592</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>648</v>
+        <v>769</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
         <v>101</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6142</v>
+        <v>4458</v>
       </c>
       <c r="C2" t="n">
-        <v>6825</v>
+        <v>7012</v>
       </c>
       <c r="D2" t="n">
-        <v>24343</v>
+        <v>25595</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5527</v>
+        <v>4064</v>
       </c>
       <c r="C3" t="n">
-        <v>4788</v>
+        <v>7149</v>
       </c>
       <c r="D3" t="n">
-        <v>18108</v>
+        <v>15589</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4380</v>
+        <v>3246</v>
       </c>
       <c r="C4" t="n">
-        <v>6980</v>
+        <v>10699</v>
       </c>
       <c r="D4" t="n">
-        <v>12183</v>
+        <v>10785</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2217</v>
+        <v>1786</v>
       </c>
       <c r="C5" t="n">
-        <v>5691</v>
+        <v>7585</v>
       </c>
       <c r="D5" t="n">
-        <v>4651</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1244</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>3226</v>
+        <v>3731</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>478</v>
       </c>
       <c r="C7" t="n">
-        <v>1667</v>
+        <v>2054</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>1114</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3589</v>
+        <v>2657</v>
       </c>
       <c r="C2" t="n">
-        <v>3082</v>
+        <v>3209</v>
       </c>
       <c r="D2" t="n">
-        <v>16847</v>
+        <v>17622</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5525</v>
+        <v>4012</v>
       </c>
       <c r="C3" t="n">
-        <v>5344</v>
+        <v>6873</v>
       </c>
       <c r="D3" t="n">
-        <v>18371</v>
+        <v>16335</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4827</v>
+        <v>3580</v>
       </c>
       <c r="C4" t="n">
-        <v>6747</v>
+        <v>10413</v>
       </c>
       <c r="D4" t="n">
-        <v>12966</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>1863</v>
       </c>
       <c r="C5" t="n">
-        <v>6815</v>
+        <v>9287</v>
       </c>
       <c r="D5" t="n">
-        <v>5063</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1061</v>
+        <v>868</v>
       </c>
       <c r="C6" t="n">
-        <v>3907</v>
+        <v>4554</v>
       </c>
       <c r="D6" t="n">
-        <v>1315</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>1727</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>743</v>
+        <v>846</v>
       </c>
       <c r="D8" t="n">
         <v>387</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4573</v>
+        <v>3287</v>
       </c>
       <c r="C2" t="n">
-        <v>8461</v>
+        <v>7447</v>
       </c>
       <c r="D2" t="n">
-        <v>14668</v>
+        <v>24090</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3983</v>
+        <v>2956</v>
       </c>
       <c r="C3" t="n">
-        <v>3795</v>
+        <v>4648</v>
       </c>
       <c r="D3" t="n">
-        <v>17063</v>
+        <v>15569</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4520</v>
+        <v>3285</v>
       </c>
       <c r="C4" t="n">
-        <v>5984</v>
+        <v>8531</v>
       </c>
       <c r="D4" t="n">
-        <v>13453</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2932</v>
+        <v>2268</v>
       </c>
       <c r="C5" t="n">
-        <v>6707</v>
+        <v>9691</v>
       </c>
       <c r="D5" t="n">
-        <v>6122</v>
+        <v>5495</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1400</v>
+        <v>1136</v>
       </c>
       <c r="C6" t="n">
-        <v>5164</v>
+        <v>6555</v>
       </c>
       <c r="D6" t="n">
-        <v>1850</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>2657</v>
+        <v>3133</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1123</v>
+        <v>1320</v>
       </c>
       <c r="D8" t="n">
         <v>409</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
         <v>101</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3131,7 +3131,7 @@
         <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3315</v>
+        <v>2349</v>
       </c>
       <c r="C2" t="n">
-        <v>4293</v>
+        <v>5016</v>
       </c>
       <c r="D2" t="n">
-        <v>11204</v>
+        <v>17148</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3661</v>
+        <v>2683</v>
       </c>
       <c r="C3" t="n">
-        <v>5153</v>
+        <v>5209</v>
       </c>
       <c r="D3" t="n">
-        <v>15847</v>
+        <v>15894</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4012</v>
+        <v>2938</v>
       </c>
       <c r="C4" t="n">
-        <v>5107</v>
+        <v>7033</v>
       </c>
       <c r="D4" t="n">
-        <v>13658</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3254</v>
+        <v>2459</v>
       </c>
       <c r="C5" t="n">
-        <v>6554</v>
+        <v>9449</v>
       </c>
       <c r="D5" t="n">
-        <v>6897</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1673</v>
+        <v>1325</v>
       </c>
       <c r="C6" t="n">
-        <v>5869</v>
+        <v>7766</v>
       </c>
       <c r="D6" t="n">
-        <v>2233</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>3476</v>
+        <v>4151</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1489</v>
+        <v>1724</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3428,7 +3428,7 @@
         <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6372</v>
+        <v>3017</v>
       </c>
       <c r="C2" t="n">
-        <v>8732</v>
+        <v>6412</v>
       </c>
       <c r="D2" t="n">
-        <v>11942</v>
+        <v>16134</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2972</v>
+        <v>2162</v>
       </c>
       <c r="C3" t="n">
-        <v>4251</v>
+        <v>4615</v>
       </c>
       <c r="D3" t="n">
-        <v>14365</v>
+        <v>15027</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3375</v>
+        <v>2477</v>
       </c>
       <c r="C4" t="n">
-        <v>5021</v>
+        <v>6133</v>
       </c>
       <c r="D4" t="n">
-        <v>13426</v>
+        <v>12328</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3240</v>
+        <v>2416</v>
       </c>
       <c r="C5" t="n">
-        <v>5806</v>
+        <v>8210</v>
       </c>
       <c r="D5" t="n">
-        <v>7660</v>
+        <v>6698</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2059</v>
+        <v>1563</v>
       </c>
       <c r="C6" t="n">
-        <v>6093</v>
+        <v>8423</v>
       </c>
       <c r="D6" t="n">
-        <v>2830</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>715</v>
+        <v>547</v>
       </c>
       <c r="C7" t="n">
-        <v>4446</v>
+        <v>5460</v>
       </c>
       <c r="D7" t="n">
-        <v>937</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>2208</v>
+        <v>2555</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>856</v>
+        <v>915</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>96</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6565</v>
+        <v>5011</v>
       </c>
       <c r="C2" t="n">
-        <v>3672</v>
+        <v>2323</v>
       </c>
       <c r="D2" t="n">
-        <v>5818</v>
+        <v>7315</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4509</v>
+        <v>2185</v>
       </c>
       <c r="C2" t="n">
-        <v>4889</v>
+        <v>3693</v>
       </c>
       <c r="D2" t="n">
-        <v>8790</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4179</v>
+        <v>2885</v>
       </c>
       <c r="C3" t="n">
-        <v>5686</v>
+        <v>5423</v>
       </c>
       <c r="D3" t="n">
-        <v>15456</v>
+        <v>16157</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4714</v>
+        <v>3496</v>
       </c>
       <c r="C4" t="n">
-        <v>7037</v>
+        <v>8931</v>
       </c>
       <c r="D4" t="n">
-        <v>13751</v>
+        <v>12613</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>1488</v>
       </c>
       <c r="C5" t="n">
-        <v>8563</v>
+        <v>11966</v>
       </c>
       <c r="D5" t="n">
-        <v>6975</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>660</v>
+        <v>505</v>
       </c>
       <c r="C6" t="n">
-        <v>5611</v>
+        <v>6919</v>
       </c>
       <c r="D6" t="n">
-        <v>2176</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2163</v>
+        <v>2503</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>896</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
         <v>94</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6748</v>
+        <v>5855</v>
       </c>
       <c r="C2" t="n">
-        <v>2330</v>
+        <v>4635</v>
       </c>
       <c r="D2" t="n">
-        <v>12762</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2789</v>
+        <v>2130</v>
       </c>
       <c r="C3" t="n">
-        <v>1880</v>
+        <v>1189</v>
       </c>
       <c r="D3" t="n">
-        <v>1663</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="4">
@@ -4666,7 +4666,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>93</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4728</v>
+        <v>4831</v>
       </c>
       <c r="C2" t="n">
-        <v>3134</v>
+        <v>6217</v>
       </c>
       <c r="D2" t="n">
-        <v>13733</v>
+        <v>29126</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3917</v>
+        <v>3324</v>
       </c>
       <c r="C3" t="n">
-        <v>1841</v>
+        <v>2732</v>
       </c>
       <c r="D3" t="n">
-        <v>3405</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1245</v>
+        <v>959</v>
       </c>
       <c r="C4" t="n">
-        <v>1162</v>
+        <v>751</v>
       </c>
       <c r="D4" t="n">
-        <v>1516</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>304</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>233</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6515</v>
+        <v>4828</v>
       </c>
       <c r="C2" t="n">
-        <v>3222</v>
+        <v>4686</v>
       </c>
       <c r="D2" t="n">
-        <v>24569</v>
+        <v>23616</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3559</v>
+        <v>3376</v>
       </c>
       <c r="C3" t="n">
-        <v>2211</v>
+        <v>4009</v>
       </c>
       <c r="D3" t="n">
-        <v>4812</v>
+        <v>7349</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2220</v>
+        <v>1812</v>
       </c>
       <c r="C4" t="n">
-        <v>1528</v>
+        <v>1850</v>
       </c>
       <c r="D4" t="n">
-        <v>1818</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>570</v>
+        <v>454</v>
       </c>
       <c r="C5" t="n">
-        <v>739</v>
+        <v>511</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
         <v>303</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>625</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
         <v>121</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6369</v>
+        <v>4901</v>
       </c>
       <c r="C2" t="n">
-        <v>4819</v>
+        <v>6239</v>
       </c>
       <c r="D2" t="n">
-        <v>23088</v>
+        <v>24057</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4078</v>
+        <v>3378</v>
       </c>
       <c r="C3" t="n">
-        <v>2381</v>
+        <v>3791</v>
       </c>
       <c r="D3" t="n">
-        <v>7476</v>
+        <v>9304</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2476</v>
+        <v>2185</v>
       </c>
       <c r="C4" t="n">
-        <v>1869</v>
+        <v>2992</v>
       </c>
       <c r="D4" t="n">
-        <v>2291</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1159</v>
+        <v>940</v>
       </c>
       <c r="C5" t="n">
-        <v>1133</v>
+        <v>1202</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>525</v>
+        <v>407</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>668</v>
@@ -5529,7 +5529,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
         <v>377</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>284</v>
@@ -5588,7 +5588,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>128</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>123</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6930</v>
+        <v>7174</v>
       </c>
       <c r="C2" t="n">
-        <v>8781</v>
+        <v>5762</v>
       </c>
       <c r="D2" t="n">
-        <v>36013</v>
+        <v>22832</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3816</v>
+        <v>3011</v>
       </c>
       <c r="C3" t="n">
-        <v>3006</v>
+        <v>4147</v>
       </c>
       <c r="D3" t="n">
-        <v>8887</v>
+        <v>10246</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2061</v>
+        <v>1726</v>
       </c>
       <c r="C4" t="n">
-        <v>1774</v>
+        <v>2799</v>
       </c>
       <c r="D4" t="n">
-        <v>2812</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>957</v>
+        <v>824</v>
       </c>
       <c r="C5" t="n">
-        <v>1118</v>
+        <v>1587</v>
       </c>
       <c r="D5" t="n">
-        <v>1159</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>361</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>74</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6338</v>
+        <v>6039</v>
       </c>
       <c r="C2" t="n">
-        <v>7256</v>
+        <v>5756</v>
       </c>
       <c r="D2" t="n">
-        <v>35855</v>
+        <v>26398</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4489</v>
+        <v>4279</v>
       </c>
       <c r="C3" t="n">
-        <v>5576</v>
+        <v>4389</v>
       </c>
       <c r="D3" t="n">
-        <v>12992</v>
+        <v>11690</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2580</v>
+        <v>2091</v>
       </c>
       <c r="C4" t="n">
-        <v>2505</v>
+        <v>3581</v>
       </c>
       <c r="D4" t="n">
-        <v>4009</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1137</v>
       </c>
       <c r="C5" t="n">
-        <v>1491</v>
+        <v>2287</v>
       </c>
       <c r="D5" t="n">
-        <v>1445</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>618</v>
+        <v>523</v>
       </c>
       <c r="C6" t="n">
-        <v>880</v>
+        <v>1149</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="D8" t="n">
         <v>384</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>82</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7480</v>
+        <v>4381</v>
       </c>
       <c r="C2" t="n">
-        <v>4019</v>
+        <v>9890</v>
       </c>
       <c r="D2" t="n">
-        <v>40217</v>
+        <v>27962</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4459</v>
+        <v>4250</v>
       </c>
       <c r="C3" t="n">
-        <v>5628</v>
+        <v>4452</v>
       </c>
       <c r="D3" t="n">
-        <v>15876</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3071</v>
+        <v>2767</v>
       </c>
       <c r="C4" t="n">
-        <v>4251</v>
+        <v>3979</v>
       </c>
       <c r="D4" t="n">
-        <v>5698</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1731</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>2020</v>
+        <v>2972</v>
       </c>
       <c r="D5" t="n">
-        <v>1893</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>912</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>1209</v>
+        <v>1758</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>681</v>
+        <v>807</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_14_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5288</v>
+        <v>1152</v>
       </c>
       <c r="C2" t="n">
-        <v>10736</v>
+        <v>2789</v>
       </c>
       <c r="D2" t="n">
-        <v>26752</v>
+        <v>10558</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3566</v>
+        <v>1872</v>
       </c>
       <c r="C3" t="n">
-        <v>6347</v>
+        <v>6812</v>
       </c>
       <c r="D3" t="n">
-        <v>14592</v>
+        <v>12180</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2974</v>
+        <v>1190</v>
       </c>
       <c r="C4" t="n">
-        <v>4155</v>
+        <v>8667</v>
       </c>
       <c r="D4" t="n">
-        <v>7081</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1818</v>
+        <v>572</v>
       </c>
       <c r="C5" t="n">
-        <v>3441</v>
+        <v>5669</v>
       </c>
       <c r="D5" t="n">
-        <v>2801</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>244</v>
       </c>
       <c r="C6" t="n">
-        <v>2356</v>
+        <v>2469</v>
       </c>
       <c r="D6" t="n">
-        <v>1161</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1274</v>
+        <v>900</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>563</v>
+        <v>365</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7685</v>
+        <v>1020</v>
       </c>
       <c r="C2" t="n">
-        <v>14582</v>
+        <v>10018</v>
       </c>
       <c r="D2" t="n">
-        <v>25140</v>
+        <v>14590</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3593</v>
+        <v>1294</v>
       </c>
       <c r="C3" t="n">
-        <v>7390</v>
+        <v>4149</v>
       </c>
       <c r="D3" t="n">
-        <v>15339</v>
+        <v>11075</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2776</v>
+        <v>1311</v>
       </c>
       <c r="C4" t="n">
-        <v>5122</v>
+        <v>7489</v>
       </c>
       <c r="D4" t="n">
-        <v>8163</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2055</v>
+        <v>758</v>
       </c>
       <c r="C5" t="n">
-        <v>3719</v>
+        <v>7159</v>
       </c>
       <c r="D5" t="n">
-        <v>3387</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>350</v>
       </c>
       <c r="C6" t="n">
-        <v>2819</v>
+        <v>4033</v>
       </c>
       <c r="D6" t="n">
-        <v>1412</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>624</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>1782</v>
+        <v>1646</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>883</v>
+        <v>604</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7893</v>
+        <v>548</v>
       </c>
       <c r="C2" t="n">
-        <v>16904</v>
+        <v>4189</v>
       </c>
       <c r="D2" t="n">
-        <v>25370</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4295</v>
+        <v>1173</v>
       </c>
       <c r="C3" t="n">
-        <v>9288</v>
+        <v>6236</v>
       </c>
       <c r="D3" t="n">
-        <v>15587</v>
+        <v>11213</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2690</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>6060</v>
+        <v>6841</v>
       </c>
       <c r="D4" t="n">
-        <v>8938</v>
+        <v>7590</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2095</v>
+        <v>756</v>
       </c>
       <c r="C5" t="n">
-        <v>4225</v>
+        <v>8166</v>
       </c>
       <c r="D5" t="n">
-        <v>4017</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1435</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>3181</v>
+        <v>5051</v>
       </c>
       <c r="D6" t="n">
-        <v>1663</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>787</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2200</v>
+        <v>1546</v>
       </c>
       <c r="D7" t="n">
-        <v>816</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1244</v>
+        <v>520</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>341</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7202</v>
+        <v>616</v>
       </c>
       <c r="C2" t="n">
-        <v>11224</v>
+        <v>8999</v>
       </c>
       <c r="D2" t="n">
-        <v>20691</v>
+        <v>15007</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5072</v>
+        <v>766</v>
       </c>
       <c r="C3" t="n">
-        <v>13600</v>
+        <v>4596</v>
       </c>
       <c r="D3" t="n">
-        <v>17227</v>
+        <v>10265</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1935</v>
+        <v>1171</v>
       </c>
       <c r="C4" t="n">
-        <v>7488</v>
+        <v>6450</v>
       </c>
       <c r="D4" t="n">
-        <v>8658</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1325</v>
+        <v>928</v>
       </c>
       <c r="C5" t="n">
-        <v>3117</v>
+        <v>7425</v>
       </c>
       <c r="D5" t="n">
-        <v>2748</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>2156</v>
+        <v>6534</v>
       </c>
       <c r="D6" t="n">
-        <v>799</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>1219</v>
+        <v>3087</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>578</v>
+        <v>932</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4288</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>4596</v>
+        <v>4221</v>
       </c>
       <c r="D2" t="n">
-        <v>16034</v>
+        <v>10644</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5171</v>
+        <v>622</v>
       </c>
       <c r="C3" t="n">
-        <v>11286</v>
+        <v>5938</v>
       </c>
       <c r="D3" t="n">
-        <v>16871</v>
+        <v>10417</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2732</v>
+        <v>960</v>
       </c>
       <c r="C4" t="n">
-        <v>10553</v>
+        <v>5665</v>
       </c>
       <c r="D4" t="n">
-        <v>9877</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>979</v>
       </c>
       <c r="C5" t="n">
-        <v>5048</v>
+        <v>7162</v>
       </c>
       <c r="D5" t="n">
-        <v>3454</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>523</v>
       </c>
       <c r="C6" t="n">
-        <v>2607</v>
+        <v>7112</v>
       </c>
       <c r="D6" t="n">
-        <v>999</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>1592</v>
+        <v>4277</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>769</v>
+        <v>1448</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4458</v>
+        <v>662</v>
       </c>
       <c r="C2" t="n">
-        <v>7012</v>
+        <v>7391</v>
       </c>
       <c r="D2" t="n">
-        <v>25595</v>
+        <v>13109</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4064</v>
+        <v>452</v>
       </c>
       <c r="C3" t="n">
-        <v>7149</v>
+        <v>4561</v>
       </c>
       <c r="D3" t="n">
-        <v>15589</v>
+        <v>9847</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3246</v>
+        <v>727</v>
       </c>
       <c r="C4" t="n">
-        <v>10699</v>
+        <v>5675</v>
       </c>
       <c r="D4" t="n">
-        <v>10785</v>
+        <v>8169</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1786</v>
+        <v>899</v>
       </c>
       <c r="C5" t="n">
-        <v>7585</v>
+        <v>6406</v>
       </c>
       <c r="D5" t="n">
-        <v>4397</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>641</v>
       </c>
       <c r="C6" t="n">
-        <v>3731</v>
+        <v>7067</v>
       </c>
       <c r="D6" t="n">
-        <v>1362</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>2054</v>
+        <v>5484</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1114</v>
+        <v>2528</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>816</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2657</v>
+        <v>455</v>
       </c>
       <c r="C2" t="n">
-        <v>3209</v>
+        <v>3962</v>
       </c>
       <c r="D2" t="n">
-        <v>17622</v>
+        <v>9543</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4012</v>
+        <v>669</v>
       </c>
       <c r="C3" t="n">
-        <v>6873</v>
+        <v>5672</v>
       </c>
       <c r="D3" t="n">
-        <v>16335</v>
+        <v>10867</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3580</v>
+        <v>1189</v>
       </c>
       <c r="C4" t="n">
-        <v>10413</v>
+        <v>7888</v>
       </c>
       <c r="D4" t="n">
-        <v>11581</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1863</v>
+        <v>642</v>
       </c>
       <c r="C5" t="n">
-        <v>9287</v>
+        <v>9629</v>
       </c>
       <c r="D5" t="n">
-        <v>4636</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>868</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>4554</v>
+        <v>7036</v>
       </c>
       <c r="D6" t="n">
-        <v>1332</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>2477</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>846</v>
+        <v>799</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3287</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>7447</v>
+        <v>3181</v>
       </c>
       <c r="D2" t="n">
-        <v>24090</v>
+        <v>7417</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2956</v>
+        <v>489</v>
       </c>
       <c r="C3" t="n">
-        <v>4648</v>
+        <v>4331</v>
       </c>
       <c r="D3" t="n">
-        <v>15569</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3285</v>
+        <v>797</v>
       </c>
       <c r="C4" t="n">
-        <v>8531</v>
+        <v>6371</v>
       </c>
       <c r="D4" t="n">
-        <v>11959</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2268</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>9691</v>
+        <v>7822</v>
       </c>
       <c r="D5" t="n">
-        <v>5495</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1136</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>6555</v>
+        <v>6668</v>
       </c>
       <c r="D6" t="n">
-        <v>1758</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>3133</v>
+        <v>3159</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1320</v>
+        <v>929</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2349</v>
+        <v>271</v>
       </c>
       <c r="C2" t="n">
-        <v>5016</v>
+        <v>7253</v>
       </c>
       <c r="D2" t="n">
-        <v>17148</v>
+        <v>8847</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2683</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>5209</v>
+        <v>3238</v>
       </c>
       <c r="D3" t="n">
-        <v>15894</v>
+        <v>8823</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2938</v>
+        <v>576</v>
       </c>
       <c r="C4" t="n">
-        <v>7033</v>
+        <v>5122</v>
       </c>
       <c r="D4" t="n">
-        <v>12160</v>
+        <v>8325</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2459</v>
+        <v>633</v>
       </c>
       <c r="C5" t="n">
-        <v>9449</v>
+        <v>6968</v>
       </c>
       <c r="D5" t="n">
-        <v>6063</v>
+        <v>4877</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1325</v>
+        <v>359</v>
       </c>
       <c r="C6" t="n">
-        <v>7766</v>
+        <v>7172</v>
       </c>
       <c r="D6" t="n">
-        <v>2111</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>4151</v>
+        <v>4908</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1724</v>
+        <v>1964</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3017</v>
+        <v>368</v>
       </c>
       <c r="C2" t="n">
-        <v>6412</v>
+        <v>9260</v>
       </c>
       <c r="D2" t="n">
-        <v>16134</v>
+        <v>10833</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2162</v>
+        <v>246</v>
       </c>
       <c r="C3" t="n">
-        <v>4615</v>
+        <v>4509</v>
       </c>
       <c r="D3" t="n">
-        <v>15027</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2477</v>
+        <v>404</v>
       </c>
       <c r="C4" t="n">
-        <v>6133</v>
+        <v>4074</v>
       </c>
       <c r="D4" t="n">
-        <v>12328</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2416</v>
+        <v>552</v>
       </c>
       <c r="C5" t="n">
-        <v>8210</v>
+        <v>5936</v>
       </c>
       <c r="D5" t="n">
-        <v>6698</v>
+        <v>5291</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1563</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>8423</v>
+        <v>7006</v>
       </c>
       <c r="D6" t="n">
-        <v>2577</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>5460</v>
+        <v>5878</v>
       </c>
       <c r="D7" t="n">
-        <v>913</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2555</v>
+        <v>3261</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>915</v>
+        <v>1151</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5011</v>
+        <v>3558</v>
       </c>
       <c r="C2" t="n">
-        <v>2323</v>
+        <v>15538</v>
       </c>
       <c r="D2" t="n">
-        <v>7315</v>
+        <v>13220</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2185</v>
+        <v>332</v>
       </c>
       <c r="C2" t="n">
-        <v>3693</v>
+        <v>12932</v>
       </c>
       <c r="D2" t="n">
-        <v>12003</v>
+        <v>15741</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2885</v>
+        <v>242</v>
       </c>
       <c r="C3" t="n">
-        <v>5423</v>
+        <v>5775</v>
       </c>
       <c r="D3" t="n">
-        <v>16157</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3496</v>
+        <v>298</v>
       </c>
       <c r="C4" t="n">
-        <v>8931</v>
+        <v>4185</v>
       </c>
       <c r="D4" t="n">
-        <v>12613</v>
+        <v>7918</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1488</v>
+        <v>453</v>
       </c>
       <c r="C5" t="n">
-        <v>11966</v>
+        <v>4951</v>
       </c>
       <c r="D5" t="n">
-        <v>6085</v>
+        <v>5492</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>505</v>
+        <v>447</v>
       </c>
       <c r="C6" t="n">
-        <v>6919</v>
+        <v>6489</v>
       </c>
       <c r="D6" t="n">
-        <v>2041</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>2503</v>
+        <v>6282</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>896</v>
+        <v>4311</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>1956</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>628</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5855</v>
+        <v>4315</v>
       </c>
       <c r="C2" t="n">
-        <v>4635</v>
+        <v>10091</v>
       </c>
       <c r="D2" t="n">
-        <v>12154</v>
+        <v>22224</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2130</v>
+        <v>1149</v>
       </c>
       <c r="C3" t="n">
-        <v>1189</v>
+        <v>6136</v>
       </c>
       <c r="D3" t="n">
-        <v>1926</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4831</v>
+        <v>2363</v>
       </c>
       <c r="C2" t="n">
-        <v>6217</v>
+        <v>5992</v>
       </c>
       <c r="D2" t="n">
-        <v>29126</v>
+        <v>21028</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3324</v>
+        <v>2314</v>
       </c>
       <c r="C3" t="n">
-        <v>2732</v>
+        <v>7287</v>
       </c>
       <c r="D3" t="n">
-        <v>3502</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>959</v>
+        <v>558</v>
       </c>
       <c r="C4" t="n">
-        <v>751</v>
+        <v>3818</v>
       </c>
       <c r="D4" t="n">
-        <v>1569</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4828</v>
+        <v>2259</v>
       </c>
       <c r="C2" t="n">
-        <v>4686</v>
+        <v>5930</v>
       </c>
       <c r="D2" t="n">
-        <v>23616</v>
+        <v>24514</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3376</v>
+        <v>1930</v>
       </c>
       <c r="C3" t="n">
-        <v>4009</v>
+        <v>5630</v>
       </c>
       <c r="D3" t="n">
-        <v>7349</v>
+        <v>7871</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1812</v>
+        <v>1243</v>
       </c>
       <c r="C4" t="n">
-        <v>1850</v>
+        <v>5803</v>
       </c>
       <c r="D4" t="n">
-        <v>1877</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>454</v>
+        <v>285</v>
       </c>
       <c r="C5" t="n">
-        <v>511</v>
+        <v>2283</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4901</v>
+        <v>1676</v>
       </c>
       <c r="C2" t="n">
-        <v>6239</v>
+        <v>9261</v>
       </c>
       <c r="D2" t="n">
-        <v>24057</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3378</v>
+        <v>1724</v>
       </c>
       <c r="C3" t="n">
-        <v>3791</v>
+        <v>5021</v>
       </c>
       <c r="D3" t="n">
-        <v>9304</v>
+        <v>9967</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2185</v>
+        <v>1367</v>
       </c>
       <c r="C4" t="n">
-        <v>2992</v>
+        <v>5530</v>
       </c>
       <c r="D4" t="n">
-        <v>2800</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>940</v>
+        <v>642</v>
       </c>
       <c r="C5" t="n">
-        <v>1202</v>
+        <v>4161</v>
       </c>
       <c r="D5" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>176</v>
       </c>
       <c r="C6" t="n">
-        <v>407</v>
+        <v>1326</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7174</v>
+        <v>2426</v>
       </c>
       <c r="C2" t="n">
-        <v>5762</v>
+        <v>6594</v>
       </c>
       <c r="D2" t="n">
-        <v>22832</v>
+        <v>19666</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3011</v>
+        <v>1409</v>
       </c>
       <c r="C3" t="n">
-        <v>4147</v>
+        <v>6243</v>
       </c>
       <c r="D3" t="n">
-        <v>10246</v>
+        <v>10724</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1726</v>
+        <v>1327</v>
       </c>
       <c r="C4" t="n">
-        <v>2799</v>
+        <v>5146</v>
       </c>
       <c r="D4" t="n">
-        <v>3382</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>824</v>
+        <v>850</v>
       </c>
       <c r="C5" t="n">
-        <v>1587</v>
+        <v>4731</v>
       </c>
       <c r="D5" t="n">
-        <v>1247</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>549</v>
+        <v>2726</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>241</v>
+        <v>800</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6039</v>
+        <v>2497</v>
       </c>
       <c r="C2" t="n">
-        <v>5756</v>
+        <v>9774</v>
       </c>
       <c r="D2" t="n">
-        <v>26398</v>
+        <v>19127</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4279</v>
+        <v>1518</v>
       </c>
       <c r="C3" t="n">
-        <v>4389</v>
+        <v>5619</v>
       </c>
       <c r="D3" t="n">
-        <v>11690</v>
+        <v>11376</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2091</v>
+        <v>1183</v>
       </c>
       <c r="C4" t="n">
-        <v>3581</v>
+        <v>5586</v>
       </c>
       <c r="D4" t="n">
-        <v>4728</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1137</v>
+        <v>934</v>
       </c>
       <c r="C5" t="n">
-        <v>2287</v>
+        <v>4831</v>
       </c>
       <c r="D5" t="n">
-        <v>1627</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C6" t="n">
-        <v>1149</v>
+        <v>3595</v>
       </c>
       <c r="D6" t="n">
-        <v>844</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C7" t="n">
-        <v>418</v>
+        <v>1686</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>232</v>
+        <v>520</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4381</v>
+        <v>2256</v>
       </c>
       <c r="C2" t="n">
-        <v>9890</v>
+        <v>6177</v>
       </c>
       <c r="D2" t="n">
-        <v>27962</v>
+        <v>15213</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4250</v>
+        <v>2042</v>
       </c>
       <c r="C3" t="n">
-        <v>4452</v>
+        <v>8966</v>
       </c>
       <c r="D3" t="n">
-        <v>13300</v>
+        <v>12537</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2767</v>
+        <v>863</v>
       </c>
       <c r="C4" t="n">
-        <v>3979</v>
+        <v>8069</v>
       </c>
       <c r="D4" t="n">
-        <v>5987</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>472</v>
       </c>
       <c r="C5" t="n">
-        <v>2972</v>
+        <v>3523</v>
       </c>
       <c r="D5" t="n">
-        <v>2172</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>1758</v>
+        <v>1652</v>
       </c>
       <c r="D6" t="n">
-        <v>966</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>807</v>
+        <v>509</v>
       </c>
       <c r="D7" t="n">
-        <v>611</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
